--- a/research/traditional_assets/database/data/switzerland/switzerland_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_brokerage_investment_banking.xlsx
@@ -588,16 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.119945</v>
+        <v>0.04679999999999999</v>
       </c>
       <c r="E2">
-        <v>0.24765</v>
-      </c>
-      <c r="F2">
-        <v>0.27</v>
+        <v>0.134</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.009211322530760437</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -609,91 +606,91 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>232.287</v>
+        <v>308.1</v>
       </c>
       <c r="L2">
-        <v>0.1669448037947391</v>
+        <v>0.2071539030457877</v>
       </c>
       <c r="M2">
-        <v>88.53</v>
+        <v>99.12</v>
       </c>
       <c r="N2">
-        <v>0.02124957995295473</v>
+        <v>0.05529707112970712</v>
       </c>
       <c r="O2">
-        <v>0.3811233517157654</v>
+        <v>0.321713729308666</v>
       </c>
       <c r="P2">
-        <v>64.2</v>
+        <v>68.2</v>
       </c>
       <c r="Q2">
-        <v>0.0154097258892996</v>
+        <v>0.03804741980474198</v>
       </c>
       <c r="R2">
-        <v>0.276382234046675</v>
+        <v>0.2213567023693606</v>
       </c>
       <c r="S2">
-        <v>24.33</v>
+        <v>30.92</v>
       </c>
       <c r="T2">
-        <v>0.2748220942053541</v>
+        <v>0.3119451170298628</v>
       </c>
       <c r="U2">
-        <v>4047.6</v>
+        <v>379.6</v>
       </c>
       <c r="V2">
-        <v>0.9715328116749076</v>
+        <v>0.2117712691771269</v>
       </c>
       <c r="W2">
-        <v>0.1561170878158619</v>
+        <v>0.1914989825910016</v>
       </c>
       <c r="X2">
-        <v>0.04011977276202662</v>
+        <v>0.0891347644860707</v>
       </c>
       <c r="Y2">
-        <v>0.1159973150538353</v>
+        <v>0.1023642181049309</v>
       </c>
       <c r="Z2">
-        <v>-0.6755680714701885</v>
+        <v>0.1158060052806853</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03389383584960778</v>
+        <v>0.0671447182976759</v>
       </c>
       <c r="AC2">
-        <v>-0.03389383584960778</v>
+        <v>-0.0671447182976759</v>
       </c>
       <c r="AD2">
-        <v>487.4</v>
+        <v>13807.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>487.4</v>
+        <v>13807.3</v>
       </c>
       <c r="AG2">
-        <v>-3560.2</v>
+        <v>13427.7</v>
       </c>
       <c r="AH2">
-        <v>0.1047361182740244</v>
+        <v>0.8850946807010346</v>
       </c>
       <c r="AI2">
-        <v>0.2926799975980303</v>
+        <v>0.9045840785654855</v>
       </c>
       <c r="AJ2">
-        <v>-5.874917491749175</v>
+        <v>0.8822288800409982</v>
       </c>
       <c r="AK2">
-        <v>1.494438148008227</v>
+        <v>0.9021506171014707</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-3.011</v>
+        <v>-2.478</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -707,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Swissquote Group Holding Ltd (SWX:SQN)</t>
+          <t>Compagnie Financière Tradition SA (SWX:CFT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,13 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.233</v>
+        <v>0.027</v>
       </c>
       <c r="E3">
-        <v>0.458</v>
-      </c>
-      <c r="F3">
-        <v>0.27</v>
+        <v>0.108</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,91 +731,94 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>169.8</v>
+        <v>84.7</v>
       </c>
       <c r="L3">
-        <v>0.3529411764705883</v>
+        <v>0.0903273968220113</v>
       </c>
       <c r="M3">
-        <v>45.7</v>
+        <v>45.12</v>
       </c>
       <c r="N3">
-        <v>0.01406500061553613</v>
+        <v>0.05280280866003512</v>
       </c>
       <c r="O3">
-        <v>0.2691401648998822</v>
+        <v>0.5327036599763872</v>
       </c>
       <c r="P3">
-        <v>24.1</v>
+        <v>39.6</v>
       </c>
       <c r="Q3">
-        <v>0.007417210390249908</v>
+        <v>0.04634289057928613</v>
       </c>
       <c r="R3">
-        <v>0.1419316843345112</v>
+        <v>0.4675324675324675</v>
       </c>
       <c r="S3">
-        <v>21.6</v>
+        <v>5.520000000000003</v>
       </c>
       <c r="T3">
-        <v>0.4726477024070022</v>
+        <v>0.1223404255319149</v>
       </c>
       <c r="U3">
-        <v>3699.6</v>
+        <v>317.2</v>
       </c>
       <c r="V3">
-        <v>1.138618736919857</v>
+        <v>0.3712112346401404</v>
       </c>
       <c r="W3">
-        <v>0.3908839779005525</v>
+        <v>0.1914989825910016</v>
       </c>
       <c r="X3">
-        <v>0.03353249309506385</v>
+        <v>0.07921364457263168</v>
       </c>
       <c r="Y3">
-        <v>0.3573514848054887</v>
+        <v>0.1122853380183699</v>
       </c>
       <c r="Z3">
-        <v>-0.184513308276444</v>
+        <v>2.058165057067603</v>
       </c>
       <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0.06395203940213723</v>
+      </c>
+      <c r="AC3">
+        <v>-0.06395203940213723</v>
+      </c>
+      <c r="AD3">
+        <v>518.2</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>518.2</v>
+      </c>
+      <c r="AG3">
+        <v>201.0000000000001</v>
+      </c>
+      <c r="AH3">
+        <v>0.3775041888249436</v>
+      </c>
+      <c r="AI3">
+        <v>0.5368279291411996</v>
+      </c>
+      <c r="AJ3">
+        <v>0.1904310753197537</v>
+      </c>
+      <c r="AK3">
+        <v>0.3101373244869619</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>-0.648</v>
+      </c>
+      <c r="AQ3">
         <v>-0</v>
-      </c>
-      <c r="AB3">
-        <v>0.03329922280725184</v>
-      </c>
-      <c r="AC3">
-        <v>-0.03329922280725184</v>
-      </c>
-      <c r="AD3">
-        <v>56.4</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>56.4</v>
-      </c>
-      <c r="AG3">
-        <v>-3643.2</v>
-      </c>
-      <c r="AH3">
-        <v>0.01706195546950629</v>
-      </c>
-      <c r="AI3">
-        <v>0.08746898263027296</v>
-      </c>
-      <c r="AJ3">
-        <v>9.246700507614213</v>
-      </c>
-      <c r="AK3">
-        <v>1.192614901139191</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Compagnie Financière Tradition SA (SWX:CFT)</t>
+          <t>Leonteq AG (SWX:LEON)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,13 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.006889999999999999</v>
-      </c>
-      <c r="E4">
-        <v>0.0373</v>
+        <v>0.217</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.02577125658389767</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -859,94 +853,91 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>62.4</v>
+        <v>208.8</v>
       </c>
       <c r="L4">
-        <v>0.06931792934903354</v>
+        <v>0.3927765237020316</v>
       </c>
       <c r="M4">
-        <v>42.83</v>
+        <v>54</v>
       </c>
       <c r="N4">
-        <v>0.04991259759934739</v>
+        <v>0.06270320483046911</v>
       </c>
       <c r="O4">
-        <v>0.6863782051282051</v>
+        <v>0.2586206896551724</v>
       </c>
       <c r="P4">
-        <v>40.1</v>
+        <v>28.6</v>
       </c>
       <c r="Q4">
-        <v>0.04673115021559259</v>
+        <v>0.03320947515095216</v>
       </c>
       <c r="R4">
-        <v>0.6426282051282052</v>
+        <v>0.1369731800766283</v>
       </c>
       <c r="S4">
-        <v>2.729999999999997</v>
+        <v>25.4</v>
       </c>
       <c r="T4">
-        <v>0.06374036890030345</v>
+        <v>0.4703703703703703</v>
       </c>
       <c r="U4">
-        <v>336.2</v>
+        <v>49.5</v>
       </c>
       <c r="V4">
-        <v>0.3917958279920755</v>
+        <v>0.05747793776126335</v>
       </c>
       <c r="W4">
-        <v>0.1561170878158619</v>
+        <v>0.2675893886966552</v>
       </c>
       <c r="X4">
-        <v>0.04011977276202662</v>
+        <v>0.4052413784782761</v>
       </c>
       <c r="Y4">
-        <v>0.1159973150538353</v>
+        <v>-0.137651989781621</v>
       </c>
       <c r="Z4">
-        <v>2.085244382673153</v>
+        <v>0.04341895699759056</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03389383584960778</v>
+        <v>0.0671447182976759</v>
       </c>
       <c r="AC4">
-        <v>-0.03389383584960778</v>
+        <v>-0.0671447182976759</v>
       </c>
       <c r="AD4">
-        <v>380.7</v>
+        <v>13208.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>380.7</v>
+        <v>13208.1</v>
       </c>
       <c r="AG4">
-        <v>44.5</v>
+        <v>13158.6</v>
       </c>
       <c r="AH4">
-        <v>0.3073135292218276</v>
+        <v>0.9387887101703709</v>
       </c>
       <c r="AI4">
-        <v>0.4497341996455995</v>
+        <v>0.9387353323714828</v>
       </c>
       <c r="AJ4">
-        <v>0.04930201639707511</v>
+        <v>0.9385725901938686</v>
       </c>
       <c r="AK4">
-        <v>0.08720360572212424</v>
+        <v>0.9385190362751951</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.611</v>
-      </c>
-      <c r="AQ4">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -965,6 +956,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.04679999999999999</v>
+      </c>
+      <c r="E5">
+        <v>0.16</v>
+      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -978,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0.08699999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="L5">
-        <v>0.008613861386138613</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1005,61 +1002,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>11.8</v>
+        <v>12.9</v>
       </c>
       <c r="V5">
-        <v>0.200339558573854</v>
+        <v>0.16796875</v>
       </c>
       <c r="W5">
-        <v>0.0008463035019455253</v>
+        <v>0.136067101584343</v>
       </c>
       <c r="X5">
-        <v>0.04646041386866034</v>
+        <v>0.0891347644860707</v>
       </c>
       <c r="Y5">
-        <v>-0.04561411036671482</v>
+        <v>0.04693233709827226</v>
       </c>
       <c r="Z5">
-        <v>0.08699397071490095</v>
+        <v>0.1250607934412562</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03420790697623555</v>
+        <v>0.06813083594759335</v>
       </c>
       <c r="AC5">
-        <v>-0.03420790697623555</v>
+        <v>-0.06813083594759335</v>
       </c>
       <c r="AD5">
-        <v>50.3</v>
+        <v>81</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>50.3</v>
+        <v>81</v>
       </c>
       <c r="AG5">
-        <v>38.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.4606227106227107</v>
+        <v>0.5133079847908745</v>
       </c>
       <c r="AI5">
-        <v>0.2890804597701149</v>
+        <v>0.354796320630749</v>
       </c>
       <c r="AJ5">
-        <v>0.3952772073921971</v>
+        <v>0.4699792960662526</v>
       </c>
       <c r="AK5">
-        <v>0.2373612823674476</v>
+        <v>0.3161559888579387</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-2.4</v>
+        <v>-1.83</v>
       </c>
       <c r="AQ5">
         <v>-0</v>

--- a/research/traditional_assets/database/data/switzerland/switzerland_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_brokerage_investment_banking.xlsx
@@ -588,112 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04679999999999999</v>
+        <v>0.0277</v>
       </c>
       <c r="E2">
-        <v>0.134</v>
+        <v>0.06755</v>
       </c>
       <c r="G2">
-        <v>0.009211322530760437</v>
+        <v>0.018011282539251</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.00754434853530891</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.004411065044518454</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.004002068854554056</v>
       </c>
       <c r="K2">
-        <v>308.1</v>
+        <v>165.6</v>
       </c>
       <c r="L2">
-        <v>0.2071539030457877</v>
+        <v>0.1125535240943383</v>
       </c>
       <c r="M2">
-        <v>99.12</v>
+        <v>134.2</v>
       </c>
       <c r="N2">
-        <v>0.05529707112970712</v>
+        <v>0.07327327327327327</v>
       </c>
       <c r="O2">
-        <v>0.321713729308666</v>
+        <v>0.8103864734299516</v>
       </c>
       <c r="P2">
-        <v>68.2</v>
+        <v>86</v>
       </c>
       <c r="Q2">
-        <v>0.03804741980474198</v>
+        <v>0.04695604695604696</v>
       </c>
       <c r="R2">
-        <v>0.2213567023693606</v>
+        <v>0.5193236714975845</v>
       </c>
       <c r="S2">
-        <v>30.92</v>
+        <v>48.2</v>
       </c>
       <c r="T2">
-        <v>0.3119451170298628</v>
+        <v>0.3591654247391953</v>
       </c>
       <c r="U2">
-        <v>379.6</v>
+        <v>672.41</v>
       </c>
       <c r="V2">
-        <v>0.2117712691771269</v>
+        <v>0.3671362271362271</v>
       </c>
       <c r="W2">
-        <v>0.1914989825910016</v>
+        <v>0.08712296983758699</v>
       </c>
       <c r="X2">
-        <v>0.0891347644860707</v>
+        <v>0.07284710532291734</v>
       </c>
       <c r="Y2">
-        <v>0.1023642181049309</v>
+        <v>0.01427586451466965</v>
       </c>
       <c r="Z2">
-        <v>0.1158060052806853</v>
+        <v>0.09977783444190058</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0671447182976759</v>
+        <v>0.05849537070960032</v>
       </c>
       <c r="AC2">
-        <v>-0.0671447182976759</v>
+        <v>-0.05595710721951733</v>
       </c>
       <c r="AD2">
-        <v>13807.3</v>
+        <v>10014.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>13807.3</v>
+        <v>10014.9</v>
       </c>
       <c r="AG2">
-        <v>13427.7</v>
+        <v>9342.49</v>
       </c>
       <c r="AH2">
-        <v>0.8850946807010346</v>
+        <v>0.8453960696920584</v>
       </c>
       <c r="AI2">
-        <v>0.9045840785654855</v>
+        <v>0.8695376600824831</v>
       </c>
       <c r="AJ2">
-        <v>0.8822288800409982</v>
+        <v>0.8360925685453451</v>
       </c>
       <c r="AK2">
-        <v>0.9021506171014707</v>
+        <v>0.861448821540439</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM2">
-        <v>-2.478</v>
+        <v>-2.56</v>
+      </c>
+      <c r="AN2">
+        <v>1533.675344563553</v>
+      </c>
+      <c r="AO2">
+        <v>3.646067415730337</v>
+      </c>
+      <c r="AP2">
+        <v>1430.702909647779</v>
       </c>
       <c r="AQ2">
-        <v>-0</v>
+        <v>-2.53515625</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Compagnie Financière Tradition SA (SWX:CFT)</t>
+          <t>Valartis Group AG (SWX:VLRT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,112 +722,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.027</v>
-      </c>
-      <c r="E3">
-        <v>0.108</v>
+        <v>0.014</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.6306818181818181</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.6306818181818181</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.36875</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.36875</v>
       </c>
       <c r="K3">
-        <v>84.7</v>
+        <v>-9</v>
       </c>
       <c r="L3">
-        <v>0.0903273968220113</v>
+        <v>-0.5113636363636364</v>
       </c>
       <c r="M3">
-        <v>45.12</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.05280280866003512</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.5327036599763872</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>39.6</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.04634289057928613</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.4675324675324675</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>5.520000000000003</v>
-      </c>
-      <c r="T3">
-        <v>0.1223404255319149</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>317.2</v>
+        <v>7.51</v>
       </c>
       <c r="V3">
-        <v>0.3712112346401404</v>
+        <v>0.1754672897196262</v>
       </c>
       <c r="W3">
-        <v>0.1914989825910016</v>
+        <v>-0.07281553398058253</v>
       </c>
       <c r="X3">
-        <v>0.07921364457263168</v>
+        <v>0.07284710532291734</v>
       </c>
       <c r="Y3">
-        <v>0.1122853380183699</v>
+        <v>-0.1456626393034999</v>
       </c>
       <c r="Z3">
-        <v>2.058165057067603</v>
+        <v>0.1343921808185706</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.04955711667684789</v>
       </c>
       <c r="AB3">
-        <v>0.06395203940213723</v>
+        <v>0.05883367316407755</v>
       </c>
       <c r="AC3">
-        <v>-0.06395203940213723</v>
+        <v>-0.009276556487229658</v>
       </c>
       <c r="AD3">
-        <v>518.2</v>
+        <v>45.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>518.2</v>
+        <v>45.7</v>
       </c>
       <c r="AG3">
-        <v>201.0000000000001</v>
+        <v>38.19</v>
       </c>
       <c r="AH3">
-        <v>0.3775041888249436</v>
+        <v>0.5163841807909605</v>
       </c>
       <c r="AI3">
-        <v>0.5368279291411996</v>
+        <v>0.2969460688758934</v>
       </c>
       <c r="AJ3">
-        <v>0.1904310753197537</v>
+        <v>0.4715396962587974</v>
       </c>
       <c r="AK3">
-        <v>0.3101373244869619</v>
+        <v>0.2608784753056903</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM3">
-        <v>-0.648</v>
+        <v>-0.8800000000000001</v>
+      </c>
+      <c r="AN3">
+        <v>6.998468606431853</v>
+      </c>
+      <c r="AO3">
+        <v>3.646067415730337</v>
+      </c>
+      <c r="AP3">
+        <v>5.848392036753446</v>
       </c>
       <c r="AQ3">
-        <v>-0</v>
+        <v>-7.374999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Leonteq AG (SWX:LEON)</t>
+          <t>Compagnie Financière Tradition SA (SWX:CFT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,10 +850,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.217</v>
+        <v>0.0277</v>
+      </c>
+      <c r="E4">
+        <v>0.119</v>
       </c>
       <c r="G4">
-        <v>0.02577125658389767</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -853,91 +868,94 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>208.8</v>
+        <v>99.5</v>
       </c>
       <c r="L4">
-        <v>0.3927765237020316</v>
+        <v>0.09198483867985578</v>
       </c>
       <c r="M4">
-        <v>54</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="N4">
-        <v>0.06270320483046911</v>
+        <v>0.06527711984841308</v>
       </c>
       <c r="O4">
-        <v>0.2586206896551724</v>
+        <v>0.692462311557789</v>
       </c>
       <c r="P4">
-        <v>28.6</v>
+        <v>45.5</v>
       </c>
       <c r="Q4">
-        <v>0.03320947515095216</v>
+        <v>0.04310753197536712</v>
       </c>
       <c r="R4">
-        <v>0.1369731800766283</v>
+        <v>0.457286432160804</v>
       </c>
       <c r="S4">
-        <v>25.4</v>
+        <v>23.40000000000001</v>
       </c>
       <c r="T4">
-        <v>0.4703703703703703</v>
+        <v>0.339622641509434</v>
       </c>
       <c r="U4">
-        <v>49.5</v>
+        <v>333.9</v>
       </c>
       <c r="V4">
-        <v>0.05747793776126335</v>
+        <v>0.3163429654192326</v>
       </c>
       <c r="W4">
-        <v>0.2675893886966552</v>
+        <v>0.2352245862884161</v>
       </c>
       <c r="X4">
-        <v>0.4052413784782761</v>
+        <v>0.06094820530394993</v>
       </c>
       <c r="Y4">
-        <v>-0.137651989781621</v>
+        <v>0.1742763809844662</v>
       </c>
       <c r="Z4">
-        <v>0.04341895699759056</v>
+        <v>1.820430831369909</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0671447182976759</v>
+        <v>0.05595710721951733</v>
       </c>
       <c r="AC4">
-        <v>-0.0671447182976759</v>
+        <v>-0.05595710721951733</v>
       </c>
       <c r="AD4">
-        <v>13208.1</v>
+        <v>301.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>13208.1</v>
+        <v>301.2</v>
       </c>
       <c r="AG4">
-        <v>13158.6</v>
+        <v>-32.69999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.9387887101703709</v>
+        <v>0.2220092872410997</v>
       </c>
       <c r="AI4">
-        <v>0.9387353323714828</v>
+        <v>0.3872460786834662</v>
       </c>
       <c r="AJ4">
-        <v>0.9385725901938686</v>
+        <v>-0.031971059835745</v>
       </c>
       <c r="AK4">
-        <v>0.9385190362751951</v>
+        <v>-0.07366523991890062</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-1.68</v>
+      </c>
+      <c r="AQ4">
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -948,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Valartis Group AG (SWX:VLRT)</t>
+          <t>Leonteq AG (SWX:LEON)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,13 +975,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.04679999999999999</v>
+        <v>0.0564</v>
       </c>
       <c r="E5">
-        <v>0.16</v>
+        <v>0.0161</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.04139784946236559</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -975,91 +993,91 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>14.6</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="L5">
-        <v>0.8111111111111111</v>
+        <v>0.2018817204301075</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>65.3</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.08906164757228587</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.8695073235685753</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>40.5</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.05523731587561374</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.5392809587217045</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>24.8</v>
+      </c>
+      <c r="T5">
+        <v>0.3797856049004594</v>
       </c>
       <c r="U5">
-        <v>12.9</v>
+        <v>331</v>
       </c>
       <c r="V5">
-        <v>0.16796875</v>
+        <v>0.4514457174031642</v>
       </c>
       <c r="W5">
-        <v>0.136067101584343</v>
+        <v>0.08712296983758699</v>
       </c>
       <c r="X5">
-        <v>0.0891347644860707</v>
+        <v>0.2571456168367358</v>
       </c>
       <c r="Y5">
-        <v>0.04693233709827226</v>
+        <v>-0.1700226469991488</v>
       </c>
       <c r="Z5">
-        <v>0.1250607934412562</v>
+        <v>0.02653238805757243</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06813083594759335</v>
+        <v>0.05849537070960032</v>
       </c>
       <c r="AC5">
-        <v>-0.06813083594759335</v>
+        <v>-0.05849537070960032</v>
       </c>
       <c r="AD5">
-        <v>81</v>
+        <v>9668</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>81</v>
+        <v>9668</v>
       </c>
       <c r="AG5">
-        <v>68.09999999999999</v>
+        <v>9337</v>
       </c>
       <c r="AH5">
-        <v>0.5133079847908745</v>
+        <v>0.9295081336768833</v>
       </c>
       <c r="AI5">
-        <v>0.354796320630749</v>
+        <v>0.9132989476468477</v>
       </c>
       <c r="AJ5">
-        <v>0.4699792960662526</v>
+        <v>0.9271911183491887</v>
       </c>
       <c r="AK5">
-        <v>0.3161559888579387</v>
+        <v>0.9105004485704257</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1.83</v>
-      </c>
-      <c r="AQ5">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
